--- a/healthcare_forms/002_training_request_for_nursing_education--healthcare_forms.xlsx
+++ b/healthcare_forms/002_training_request_for_nursing_education--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Training Request For Nursing Education</t>
+          <t>What is the title of the training request?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Briefly describe the training session</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,109 +584,109 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A Training Request for Nursing Education is a form template designed to streamline the process of requesting and organizing training sessions for nursing staff. Easily customize this template to fit your specific needs and ensure efficient communication between administrators and staff. Simplify your training process with Jotform's user-friendly form templates.</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_description_2</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A Training Request for Nursing Education is a form template designed to streamline the process of requesting and organizing training sessions for nursing staff. Easily customize this template to fit your specific needs and ensure efficient communication between administrators and staff. Simplify your training process with Jotform's user-friendly form templates.</t>
+          <t>Date of the training session</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_description_3</t>
+          <t>attendees</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ensure efficient communication between administrators and staff</t>
+          <t>How many nurses are expected to attend this training session?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Is there any other information about this training session?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_description_4</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Simplify your training process with Jotform's user-friendly form templates.</t>
+          <t>Can we use your feedback for quality improvement?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,384 +704,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_title_2</t>
+          <t>other_session</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Training Request For Nursing Education</t>
+          <t>Is there any other training sessions scheduled during the same period?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>form_category</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>form_description_5</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Easily customize this template to fit your specific needs and ensure efficient communication between administrators and staff.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>form_description_6</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ensure efficient communication between administrators and staff.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_description_7</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>This template is designed to streamline the process of requesting and organizing training sessions for nursing staff.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_description_8</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Request and organize training sessions for nursing staff with this template.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_description_9</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Customize this template to fit your specific needs and ensure efficient communication between administrators and staff.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_description_10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Jotform's user-friendly form templates will help simplify your training process.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_description_11</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Simplify your training process with Jotform's user-friendly form templates.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_description_12</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Use this template to request and organize training sessions for nursing staff.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_description_13</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>A template designed to streamline the process of requesting and organizing training sessions for nursing staff.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_description_14</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Customize and use this template for your specific needs.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_description_15</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>This template is for requesting and organizing training sessions for nursing staff.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_description_16</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Use this template to simplify your training process.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_title_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Training Request For Nursing Education</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>description_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>A Training Request for Nursing Education template designed to streamline the process of requesting and organizing training sessions for nursing staff.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_forms'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare Forms'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'other_forms'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Other Forms'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1182,46 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>form_category_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'label':_'healthcare_forms'}</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'label': 'Healthcare Forms'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>form_category_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'label':_'other_forms'}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'label': 'Other Forms'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
